--- a/artfynd/A 36943-2025 artfynd.xlsx
+++ b/artfynd/A 36943-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1081,6 +1081,208 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127344489</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>560261</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7045526</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127344490</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>560205</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7045536</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36943-2025 artfynd.xlsx
+++ b/artfynd/A 36943-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>127344489</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>127344490</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 36943-2025 artfynd.xlsx
+++ b/artfynd/A 36943-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>127344489</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>127344490</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 36943-2025 artfynd.xlsx
+++ b/artfynd/A 36943-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>127344489</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>127344490</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 36943-2025 artfynd.xlsx
+++ b/artfynd/A 36943-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>127344489</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>127344490</v>
       </c>
       <c r="B7" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
